--- a/assessment_forms/026_travel_package_experience_assessment--assessment_forms.xlsx
+++ b/assessment_forms/026_travel_package_experience_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>preface_page</t>
+          <t>introduction_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -548,33 +548,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Overall Rating</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rating_page_2</t>
+          <t>section_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Overall Rating</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What did you enjoy most about the trip?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of what you enjoyed most about the trip.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating_page_3</t>
+          <t>section_1_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Activities</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,20 +611,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rating_page_4</t>
+          <t>section_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Overall Rating</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What did you least enjoy about the trip?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of what you least enjoyed about the trip.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,17 +638,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>section_2_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What did you like?</t>
+          <t>Section 2 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,15 +666,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>section_1_1</t>
+          <t>section_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Activities</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What type of transportation did you use during the trip?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +688,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>section_1_2</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or suggestions for improving the experience.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>submission_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What did you dislike?</t>
+          <t>Submission</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,205 +738,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>section_2_1</t>
+          <t>confirmation_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Activities</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>section_2_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>submission_page</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submission_page_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>confirmation_page</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>confirmation_page_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submission_page_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>submission_page_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,12 +769,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1-3_(poor)'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1-3 (poor)'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -987,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'2-3_(fair)'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '2-3 (fair)'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1004,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'3-3_(good)'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '3-3 (good)'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1021,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'4_(very_good)'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '4 (very good)'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1038,539 +870,233 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'5_(excellent)'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '5 (excellent)'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rating_page_2_choices</t>
+          <t>section_1_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1-3_(poor)'}</t>
+          <t>guided_hikes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1-3 (poor)'}</t>
+          <t>Guided Hikes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rating_page_2_choices</t>
+          <t>section_1_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'2-3_(fair)'}</t>
+          <t>kayak_or_canoe_trips</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '2-3 (fair)'}</t>
+          <t>Kayak or Canoe Trips</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rating_page_2_choices</t>
+          <t>section_1_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'3-3_(good)'}</t>
+          <t>scenic_flights</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '3-3 (good)'}</t>
+          <t>Scenic Flights</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rating_page_2_choices</t>
+          <t>section_1_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'4_(very_good)'}</t>
+          <t>wildlife_tours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '4 (very good)'}</t>
+          <t>Wildlife Tours</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rating_page_2_choices</t>
+          <t>section_1_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'5_(excellent)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '5 (excellent)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rating_page_3_choices</t>
+          <t>section_2_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1-3_(poor)'}</t>
+          <t>guided_hikes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1-3 (poor)'}</t>
+          <t>Guided Hikes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rating_page_3_choices</t>
+          <t>section_2_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'2-3_(fair)'}</t>
+          <t>kayak_or_canoe_trips</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '2-3 (fair)'}</t>
+          <t>Kayak or Canoe Trips</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rating_page_3_choices</t>
+          <t>section_2_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'3-3_(good)'}</t>
+          <t>scenic_flights</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '3-3 (good)'}</t>
+          <t>Scenic Flights</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rating_page_3_choices</t>
+          <t>section_2_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'4_(very_good)'}</t>
+          <t>wildlife_tours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '4 (very good)'}</t>
+          <t>Wildlife Tours</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rating_page_3_choices</t>
+          <t>section_2_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'5_(excellent)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '5 (excellent)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rating_page_4_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1-3_(poor)'}</t>
+          <t>guided_transportation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1-3 (poor)'}</t>
+          <t>Guided Transportation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rating_page_4_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'2-3_(fair)'}</t>
+          <t>self-guided_transportation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '2-3 (fair)'}</t>
+          <t>Self-Guided Transportation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rating_page_4_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'3-3_(good)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '3-3 (good)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>rating_page_4_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'4_(very_good)'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': '4 (very good)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>rating_page_4_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'5_(excellent)'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': '5 (excellent)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>section_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'guided_hikes'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Guided hikes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>section_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'kayak_or_canoe_trips'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Kayak or canoe trips'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>section_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'scenic_flights'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Scenic flights'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>section_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'wildlife_tours'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Wildlife tours'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>section_1_1_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': 'Other (please specify)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>section_1_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'guided_transportation'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Guided transportation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>section_1_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'self-guided_transportation'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Self-guided transportation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>section_1_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Other (please specify)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>section_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'guided_hikes'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Guided hikes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>section_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'kayak_or_canoe_trips'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Kayak or canoe trips'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>section_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'scenic_flights'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Scenic flights'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>section_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'wildlife_tours'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Wildlife tours'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>section_2_1_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': 'Other (please specify)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>section_2_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'guided_transportation'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Guided transportation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>section_2_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'self-guided_transportation'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Self-guided transportation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>section_2_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
